--- a/diseases/d011/2010-2014.xlsx
+++ b/diseases/d011/2010-2014.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26272,7 +26272,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27508,7 +27508,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -29832,7 +29832,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -32700,7 +32700,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -33788,7 +33788,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -34876,7 +34876,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -37200,7 +37200,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -38288,7 +38288,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -39376,7 +39376,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -41056,7 +41056,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -42736,7 +42736,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -44712,7 +44712,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -46392,7 +46392,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -48616,7 +48616,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -50296,7 +50296,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52272,7 +52272,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -53952,7 +53952,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -55928,7 +55928,7 @@
       </c>
       <c r="AJ316" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK316" t="inlineStr">
@@ -57608,7 +57608,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -59436,7 +59436,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -61264,7 +61264,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -63092,7 +63092,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -64920,7 +64920,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -66748,7 +66748,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -68576,7 +68576,7 @@
       </c>
       <c r="AJ392" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK392" t="inlineStr">
@@ -70948,7 +70948,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -72776,7 +72776,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -74604,7 +74604,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -76284,7 +76284,7 @@
       </c>
       <c r="AJ438" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK438" t="inlineStr">
@@ -78260,7 +78260,7 @@
       </c>
       <c r="AJ450" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK450" t="inlineStr">
@@ -79940,7 +79940,7 @@
       </c>
       <c r="AJ460" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK460" t="inlineStr">
@@ -81620,7 +81620,7 @@
       </c>
       <c r="AJ470" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK470" t="inlineStr">
@@ -83448,7 +83448,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">
@@ -85276,7 +85276,7 @@
       </c>
       <c r="AJ492" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK492" t="inlineStr">
@@ -87252,7 +87252,7 @@
       </c>
       <c r="AJ504" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK504" t="inlineStr">
@@ -88932,7 +88932,7 @@
       </c>
       <c r="AJ514" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK514" t="inlineStr">

--- a/diseases/d011/2010-2014.xlsx
+++ b/diseases/d011/2010-2014.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -26272,7 +26272,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27508,7 +27508,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -28744,7 +28744,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -29832,7 +29832,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -32700,7 +32700,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -33788,7 +33788,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -34876,7 +34876,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -37200,7 +37200,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -38288,7 +38288,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -39376,7 +39376,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -41056,7 +41056,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -42736,7 +42736,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -44712,7 +44712,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -46392,7 +46392,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -48616,7 +48616,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -50296,7 +50296,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -52272,7 +52272,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -53952,7 +53952,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -55928,7 +55928,7 @@
       </c>
       <c r="AJ316" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK316" t="inlineStr">
@@ -57608,7 +57608,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -59436,7 +59436,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -61264,7 +61264,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -63092,7 +63092,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -64920,7 +64920,7 @@
       </c>
       <c r="AJ370" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK370" t="inlineStr">
@@ -66748,7 +66748,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -68576,7 +68576,7 @@
       </c>
       <c r="AJ392" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK392" t="inlineStr">
@@ -70948,7 +70948,7 @@
       </c>
       <c r="AJ406" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK406" t="inlineStr">
@@ -72776,7 +72776,7 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
@@ -74604,7 +74604,7 @@
       </c>
       <c r="AJ428" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK428" t="inlineStr">
@@ -76284,7 +76284,7 @@
       </c>
       <c r="AJ438" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK438" t="inlineStr">
@@ -78260,7 +78260,7 @@
       </c>
       <c r="AJ450" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK450" t="inlineStr">
@@ -79940,7 +79940,7 @@
       </c>
       <c r="AJ460" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK460" t="inlineStr">
@@ -81620,7 +81620,7 @@
       </c>
       <c r="AJ470" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK470" t="inlineStr">
@@ -83448,7 +83448,7 @@
       </c>
       <c r="AJ481" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK481" t="inlineStr">
@@ -85276,7 +85276,7 @@
       </c>
       <c r="AJ492" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK492" t="inlineStr">
@@ -87252,7 +87252,7 @@
       </c>
       <c r="AJ504" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK504" t="inlineStr">
@@ -88932,7 +88932,7 @@
       </c>
       <c r="AJ514" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK514" t="inlineStr">

--- a/diseases/d011/2010-2014.xlsx
+++ b/diseases/d011/2010-2014.xlsx
@@ -1309,9 +1309,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1853,9 +1850,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2941,9 +2935,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -4029,9 +4020,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -5117,9 +5105,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.01864506151518533</v>
       </c>
@@ -6353,9 +6338,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -7441,9 +7423,6 @@
       <c r="O39" t="n">
         <v>2</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.03729012303037066</v>
       </c>
@@ -8677,9 +8656,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9913,9 +9889,6 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.01864506151518533</v>
       </c>
@@ -11149,9 +11122,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12237,9 +12207,6 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.01864506151518533</v>
       </c>
@@ -13325,9 +13292,6 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.01864506151518533</v>
       </c>
@@ -14413,9 +14377,6 @@
       <c r="O78" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.03729012303037066</v>
       </c>
@@ -15501,9 +15462,6 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -16045,9 +16003,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -17133,9 +17088,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -18221,9 +18173,6 @@
       <c r="O99" t="n">
         <v>2</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.03711786462409532</v>
       </c>
@@ -19457,9 +19406,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -20693,9 +20639,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -21929,9 +21872,6 @@
       <c r="O120" t="n">
         <v>2</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.03711786462409532</v>
       </c>
@@ -23017,9 +22957,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -24105,9 +24042,6 @@
       <c r="O132" t="n">
         <v>2</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.03711786462409532</v>
       </c>
@@ -25193,9 +25127,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -26429,9 +26360,6 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -27665,9 +27593,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -28901,9 +28826,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -29989,9 +29911,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -30533,9 +30452,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -31621,9 +31537,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -32857,9 +32770,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -33945,9 +33855,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -35033,9 +34940,6 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -36269,9 +36173,6 @@
       <c r="O200" t="n">
         <v>1</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -37357,9 +37258,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -38445,9 +38343,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -39533,9 +39428,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -41213,9 +41105,6 @@
       <c r="O228" t="n">
         <v>1</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -42893,9 +42782,6 @@
       <c r="O238" t="n">
         <v>1</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -44869,9 +44755,6 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
@@ -46549,9 +46432,6 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0</v>
       </c>
@@ -47093,9 +46973,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -48773,9 +48650,6 @@
       <c r="O273" t="n">
         <v>1</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -50453,9 +50327,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -52429,9 +52300,6 @@
       <c r="O295" t="n">
         <v>1</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -54109,9 +53977,6 @@
       <c r="O305" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0</v>
       </c>
@@ -56085,9 +55950,6 @@
       <c r="O317" t="n">
         <v>1</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -57765,9 +57627,6 @@
       <c r="O327" t="n">
         <v>3</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.0551566605436645</v>
       </c>
@@ -59593,9 +59452,6 @@
       <c r="O338" t="n">
         <v>1</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -61421,9 +61277,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -63249,9 +63102,6 @@
       <c r="O360" t="n">
         <v>0</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0</v>
       </c>
@@ -65077,9 +64927,6 @@
       <c r="O371" t="n">
         <v>3</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0.0551566605436645</v>
       </c>
@@ -66905,9 +66752,6 @@
       <c r="O382" t="n">
         <v>1</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -68733,9 +68577,6 @@
       <c r="O393" t="n">
         <v>0</v>
       </c>
-      <c r="Q393" t="n">
-        <v>0</v>
-      </c>
       <c r="R393" t="n">
         <v>0</v>
       </c>
@@ -69277,9 +69118,6 @@
       <c r="O396" t="n">
         <v>0</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>0</v>
       </c>
@@ -71105,9 +70943,6 @@
       <c r="O407" t="n">
         <v>0</v>
       </c>
-      <c r="Q407" t="n">
-        <v>0</v>
-      </c>
       <c r="R407" t="n">
         <v>0</v>
       </c>
@@ -72933,9 +72768,6 @@
       <c r="O418" t="n">
         <v>0</v>
       </c>
-      <c r="Q418" t="n">
-        <v>0</v>
-      </c>
       <c r="R418" t="n">
         <v>0</v>
       </c>
@@ -74761,9 +74593,6 @@
       <c r="O429" t="n">
         <v>1</v>
       </c>
-      <c r="Q429" t="n">
-        <v>0</v>
-      </c>
       <c r="R429" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -76441,9 +76270,6 @@
       <c r="O439" t="n">
         <v>0</v>
       </c>
-      <c r="Q439" t="n">
-        <v>0</v>
-      </c>
       <c r="R439" t="n">
         <v>0</v>
       </c>
@@ -78417,9 +78243,6 @@
       <c r="O451" t="n">
         <v>0</v>
       </c>
-      <c r="Q451" t="n">
-        <v>0</v>
-      </c>
       <c r="R451" t="n">
         <v>0</v>
       </c>
@@ -80097,9 +79920,6 @@
       <c r="O461" t="n">
         <v>2</v>
       </c>
-      <c r="Q461" t="n">
-        <v>0</v>
-      </c>
       <c r="R461" t="n">
         <v>0.03661874249773513</v>
       </c>
@@ -81777,9 +81597,6 @@
       <c r="O471" t="n">
         <v>2</v>
       </c>
-      <c r="Q471" t="n">
-        <v>0</v>
-      </c>
       <c r="R471" t="n">
         <v>0.03661874249773513</v>
       </c>
@@ -83605,9 +83422,6 @@
       <c r="O482" t="n">
         <v>1</v>
       </c>
-      <c r="Q482" t="n">
-        <v>0</v>
-      </c>
       <c r="R482" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -85433,9 +85247,6 @@
       <c r="O493" t="n">
         <v>1</v>
       </c>
-      <c r="Q493" t="n">
-        <v>0</v>
-      </c>
       <c r="R493" t="n">
         <v>0.01830937124886756</v>
       </c>
@@ -87409,9 +87220,6 @@
       <c r="O505" t="n">
         <v>0</v>
       </c>
-      <c r="Q505" t="n">
-        <v>0</v>
-      </c>
       <c r="R505" t="n">
         <v>0</v>
       </c>
@@ -89088,9 +88896,6 @@
       </c>
       <c r="O515" t="n">
         <v>4</v>
-      </c>
-      <c r="Q515" t="n">
-        <v>0</v>
       </c>
       <c r="R515" t="n">
         <v>0.07323748499547025</v>
